--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.16073239011119</v>
+        <v>7.826119013393068</v>
       </c>
       <c r="D2" t="n">
-        <v>30.47954142112894</v>
+        <v>4.952925480933452</v>
       </c>
       <c r="E2" t="n">
-        <v>4.456116033341093</v>
+        <v>0.7241188554179279</v>
       </c>
       <c r="F2" t="n">
-        <v>12.65825133724588</v>
+        <v>2.056965842302455</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.248500323429</v>
+        <v>6.377881302557213</v>
       </c>
       <c r="D3" t="n">
-        <v>5.163038746637177</v>
+        <v>0.8389937963285413</v>
       </c>
       <c r="E3" t="n">
-        <v>4.456116033341093</v>
+        <v>0.7241188554179279</v>
       </c>
       <c r="F3" t="n">
-        <v>12.65825133724588</v>
+        <v>2.056965842302455</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
